--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683C1722-FF48-4E2D-9658-A1400E5463B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF56B42-0710-48B8-8700-1BBDDEEE6CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -28,15 +28,9 @@
     <t>ЛР 3</t>
   </si>
   <si>
-    <t>SimpleMVP (users)</t>
-  </si>
-  <si>
     <t>Экстрим. Сем. 1</t>
   </si>
   <si>
-    <t>WinForms ZZ</t>
-  </si>
-  <si>
     <t>Экстрим. Сем. 2</t>
   </si>
   <si>
@@ -119,6 +113,9 @@
   </si>
   <si>
     <t>Шамарин Кирилл</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -171,7 +168,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -255,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -271,13 +268,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -290,13 +283,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -603,19 +593,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" customWidth="1"/>
     <col min="2" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="16.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -627,541 +615,504 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-    </row>
-    <row r="2" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="B2" s="4">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="12"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="12"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="14"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="13"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="E5" s="12"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="12"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="12"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="15"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="6">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="12"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
+      <c r="E11" s="12"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="12"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="12"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="4"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="6">
+        <v>3</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4</v>
+      </c>
+      <c r="E14" s="12"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2</v>
+      </c>
+      <c r="D15" s="4">
+        <v>4</v>
+      </c>
+      <c r="E15" s="12"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="12"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="16"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4">
+        <v>3</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="12"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="4"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="6">
+        <v>2</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2</v>
+      </c>
+      <c r="E18" s="12"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="16"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
+      <c r="E19" s="12"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="16"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="6">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6">
+        <v>4</v>
+      </c>
+      <c r="E20" s="12"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="4">
+        <v>5</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="12"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="16"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="6">
+        <v>3</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6">
+        <v>4</v>
+      </c>
+      <c r="E22" s="12"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="4">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="12"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" spans="1:16" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="6">
+        <v>5</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3</v>
+      </c>
+      <c r="E24" s="12"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" spans="1:16" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="4">
+        <v>3</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2</v>
+      </c>
+      <c r="E25" s="12"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="6">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2</v>
+      </c>
+      <c r="E26" s="12"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:16" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+    </row>
+    <row r="27" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="4">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4">
+        <v>2</v>
+      </c>
+      <c r="D27" s="4">
+        <v>3</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF56B42-0710-48B8-8700-1BBDDEEE6CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13D1B4C-5C23-42E3-966E-D6C96AEF4124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t>.</t>
+  </si>
+  <si>
+    <t>Графики</t>
+  </si>
+  <si>
+    <t>БД</t>
   </si>
 </sst>
 </file>
@@ -252,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -287,6 +293,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -593,17 +602,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" customWidth="1"/>
-    <col min="2" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="17" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="11.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -615,16 +627,22 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
@@ -637,13 +655,17 @@
       <c r="D2" s="4">
         <v>2</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E2" s="4">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
@@ -656,13 +678,17 @@
       <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E3" s="6">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -675,13 +701,17 @@
       <c r="D4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
@@ -694,13 +724,17 @@
       <c r="D5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
@@ -713,13 +747,17 @@
       <c r="D6" s="6">
         <v>2</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E6" s="6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
@@ -732,13 +770,17 @@
       <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
@@ -751,13 +793,17 @@
       <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="6">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
@@ -770,13 +816,17 @@
       <c r="D9" s="4">
         <v>2</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E9" s="4">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
@@ -789,13 +839,17 @@
       <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E10" s="6">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -808,13 +862,17 @@
       <c r="D11" s="4">
         <v>2</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
@@ -827,13 +885,17 @@
       <c r="D12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E12" s="6">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
@@ -846,13 +908,17 @@
       <c r="D13" s="4">
         <v>2</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>18</v>
       </c>
@@ -865,13 +931,17 @@
       <c r="D14" s="6">
         <v>4</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>19</v>
       </c>
@@ -884,13 +954,17 @@
       <c r="D15" s="4">
         <v>4</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>20</v>
       </c>
@@ -903,13 +977,17 @@
       <c r="D16" s="6">
         <v>2</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
@@ -922,13 +1000,17 @@
       <c r="D17" s="4">
         <v>2</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>22</v>
       </c>
@@ -941,13 +1023,17 @@
       <c r="D18" s="6">
         <v>2</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>23</v>
       </c>
@@ -960,13 +1046,17 @@
       <c r="D19" s="4">
         <v>2</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>24</v>
       </c>
@@ -979,13 +1069,17 @@
       <c r="D20" s="6">
         <v>4</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E20" s="6">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>25</v>
       </c>
@@ -998,13 +1092,17 @@
       <c r="D21" s="4">
         <v>3</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E21" s="4">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>26</v>
       </c>
@@ -1017,13 +1115,17 @@
       <c r="D22" s="6">
         <v>4</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E22" s="6">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>27</v>
       </c>
@@ -1036,13 +1138,17 @@
       <c r="D23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E23" s="4">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>28</v>
       </c>
@@ -1055,13 +1161,17 @@
       <c r="D24" s="6">
         <v>3</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E24" s="6">
+        <v>2</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>29</v>
       </c>
@@ -1074,13 +1184,17 @@
       <c r="D25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E25" s="4">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>30</v>
       </c>
@@ -1093,11 +1207,15 @@
       <c r="D26" s="6">
         <v>2</v>
       </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="6">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>31</v>
       </c>
@@ -1110,9 +1228,13 @@
       <c r="D27" s="4">
         <v>3</v>
       </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="E27" s="4">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13D1B4C-5C23-42E3-966E-D6C96AEF4124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE2198D-A634-4C98-8D05-25C8FC4EA7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -854,7 +854,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4">
         <v>2</v>
@@ -863,7 +863,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="12"/>
@@ -946,7 +946,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4">
         <v>2</v>
@@ -1087,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="4">
         <v>3</v>
@@ -1133,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>32</v>
@@ -1156,13 +1156,13 @@
         <v>5</v>
       </c>
       <c r="C24" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="6">
         <v>3</v>
       </c>
       <c r="E24" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="12"/>
@@ -1179,10 +1179,10 @@
         <v>3</v>
       </c>
       <c r="C25" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4">
         <v>4</v>
@@ -1223,7 +1223,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE2198D-A634-4C98-8D05-25C8FC4EA7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA77D8-0B6A-453C-8632-9291E3E6862D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>БД</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
 </sst>
 </file>
@@ -658,7 +661,9 @@
       <c r="E2" s="4">
         <v>2</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="4">
+        <v>3</v>
+      </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -681,7 +686,9 @@
       <c r="E3" s="6">
         <v>2</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G3" s="12"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -704,7 +711,9 @@
       <c r="E4" s="4">
         <v>2</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G4" s="13"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -727,7 +736,9 @@
       <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G5" s="12"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -750,7 +761,9 @@
       <c r="E6" s="6">
         <v>2</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
       <c r="G6" s="12"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -773,7 +786,9 @@
       <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4">
+        <v>4</v>
+      </c>
       <c r="G7" s="12"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -796,7 +811,9 @@
       <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G8" s="12"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -819,7 +836,9 @@
       <c r="E9" s="4">
         <v>3</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="12"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -842,7 +861,9 @@
       <c r="E10" s="6">
         <v>3</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4">
+        <v>2</v>
+      </c>
       <c r="G10" s="12"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -865,7 +886,9 @@
       <c r="E11" s="4">
         <v>3</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4">
+        <v>3</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -888,7 +911,9 @@
       <c r="E12" s="6">
         <v>4</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
@@ -911,7 +936,9 @@
       <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G13" s="12"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -934,7 +961,9 @@
       <c r="E14" s="6">
         <v>2</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="4">
+        <v>5</v>
+      </c>
       <c r="G14" s="12"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -957,7 +986,9 @@
       <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G15" s="12"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -980,7 +1011,9 @@
       <c r="E16" s="6">
         <v>2</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G16" s="12"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
@@ -1003,7 +1036,9 @@
       <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
       <c r="G17" s="12"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1026,7 +1061,9 @@
       <c r="E18" s="6">
         <v>2</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G18" s="12"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -1049,7 +1086,9 @@
       <c r="E19" s="4">
         <v>2</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G19" s="12"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1072,7 +1111,9 @@
       <c r="E20" s="6">
         <v>2</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="4">
+        <v>2</v>
+      </c>
       <c r="G20" s="12"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -1095,7 +1136,9 @@
       <c r="E21" s="4">
         <v>3</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G21" s="12"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1118,7 +1161,9 @@
       <c r="E22" s="6">
         <v>2</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G22" s="12"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -1141,7 +1186,9 @@
       <c r="E23" s="4">
         <v>2</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G23" s="12"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1164,7 +1211,9 @@
       <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G24" s="12"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -1187,7 +1236,9 @@
       <c r="E25" s="4">
         <v>4</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="4">
+        <v>3</v>
+      </c>
       <c r="G25" s="12"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1210,7 +1261,9 @@
       <c r="E26" s="6">
         <v>2</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="4">
+        <v>5</v>
+      </c>
       <c r="G26" s="12"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -1231,9 +1284,13 @@
       <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G27" s="12"/>
-      <c r="H27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="I27" s="4"/>
     </row>
   </sheetData>

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA77D8-0B6A-453C-8632-9291E3E6862D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE4A257-B73D-4B8C-89BA-A75E375D4568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -686,8 +686,8 @@
       <c r="E3" s="6">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
+      <c r="F3" s="4">
+        <v>3</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="6"/>
@@ -736,8 +736,8 @@
       <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>32</v>
+      <c r="F5" s="4">
+        <v>4</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="4"/>
@@ -805,14 +805,14 @@
       <c r="C8" s="6">
         <v>2</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>32</v>
+      <c r="D8" s="6">
+        <v>3</v>
       </c>
       <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>32</v>
+      <c r="F8" s="4">
+        <v>4</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="6"/>
@@ -905,14 +905,14 @@
       <c r="C12" s="6">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>32</v>
+      <c r="D12" s="6">
+        <v>3</v>
       </c>
       <c r="E12" s="6">
         <v>4</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>32</v>
+      <c r="F12" s="4">
+        <v>3</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="6"/>
@@ -936,8 +936,8 @@
       <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>32</v>
+      <c r="F13" s="4">
+        <v>3</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="4"/>
@@ -978,7 +978,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4">
         <v>4</v>
@@ -986,8 +986,8 @@
       <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>32</v>
+      <c r="F15" s="4">
+        <v>4</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="4"/>
@@ -1034,10 +1034,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="4"/>
@@ -1061,8 +1061,8 @@
       <c r="E18" s="6">
         <v>2</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>32</v>
+      <c r="F18" s="4">
+        <v>4</v>
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="6"/>
@@ -1136,8 +1136,8 @@
       <c r="E21" s="4">
         <v>3</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>32</v>
+      <c r="F21" s="4">
+        <v>5</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="4"/>
@@ -1153,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
@@ -1161,8 +1161,8 @@
       <c r="E22" s="6">
         <v>2</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>32</v>
+      <c r="F22" s="4">
+        <v>5</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="6"/>
@@ -1211,8 +1211,8 @@
       <c r="E24" s="6">
         <v>3</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>32</v>
+      <c r="F24" s="4">
+        <v>4</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="6"/>
@@ -1284,8 +1284,8 @@
       <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>32</v>
+      <c r="F27" s="4">
+        <v>4</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="4" t="s">

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE4A257-B73D-4B8C-89BA-A75E375D4568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="П-30 2025" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -130,7 +129,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -319,9 +318,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -359,9 +358,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -396,7 +395,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -431,7 +430,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -604,7 +603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -684,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4">
         <v>3</v>
@@ -840,7 +839,9 @@
         <v>32</v>
       </c>
       <c r="G9" s="12"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -959,7 +960,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="4">
         <v>5</v>
@@ -984,7 +985,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4">
         <v>4</v>
@@ -1140,7 +1141,9 @@
         <v>5</v>
       </c>
       <c r="G21" s="12"/>
-      <c r="H21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1159,7 +1162,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="4">
         <v>5</v>
@@ -1215,7 +1218,9 @@
         <v>4</v>
       </c>
       <c r="G24" s="12"/>
-      <c r="H24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="I24" s="6"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1259,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="4">
         <v>5</v>
@@ -1294,7 +1299,7 @@
       <c r="I27" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
+  <sortState ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1303,7 +1308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1313,7 +1318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -941,7 +941,9 @@
         <v>3</v>
       </c>
       <c r="G13" s="12"/>
-      <c r="H13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F7EB68-2DC9-4320-B735-62FFC595DB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="П-30 2025" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -129,7 +130,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -318,9 +319,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -358,9 +359,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -395,7 +396,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -430,7 +431,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -603,7 +604,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -658,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4">
         <v>3</v>
@@ -710,8 +711,8 @@
       <c r="E4" s="4">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>32</v>
+      <c r="F4" s="4">
+        <v>3</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="4"/>
@@ -1257,7 +1258,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" s="6">
         <v>2</v>
@@ -1301,7 +1302,7 @@
       <c r="I27" s="4"/>
     </row>
   </sheetData>
-  <sortState ref="A2:A25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1310,7 +1311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1320,7 +1321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Состояние МДК 01.01.xlsx
+++ b/Состояние МДК 01.01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F7EB68-2DC9-4320-B735-62FFC595DB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8C15CE-A542-44DE-9990-2CA35FBB3A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,12 +12,23 @@
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>ЛР 1</t>
   </si>
@@ -125,6 +136,12 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>20 минут</t>
+  </si>
+  <si>
+    <t>16 минут</t>
   </si>
 </sst>
 </file>
@@ -653,10 +670,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="4">
         <v>3</v>
@@ -675,10 +692,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="6">
         <v>2</v>
@@ -700,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
@@ -728,13 +745,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4">
         <v>4</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4">
         <v>4</v>
@@ -775,16 +792,16 @@
         <v>11</v>
       </c>
       <c r="B7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4">
         <v>4</v>
@@ -803,7 +820,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6">
         <v>3</v>
@@ -880,10 +897,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4">
         <v>3</v>
@@ -902,10 +919,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6">
         <v>3</v>
@@ -994,8 +1011,12 @@
         <v>4</v>
       </c>
       <c r="G15" s="12"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
@@ -1171,8 +1192,12 @@
         <v>5</v>
       </c>
       <c r="G22" s="12"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="H22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
@@ -1190,7 +1215,7 @@
         <v>32</v>
       </c>
       <c r="E23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>32</v>
